--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81133807</v>
+        <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>80433</v>
+        <v>83349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marktjärn, Mpd</t>
+          <t>Matsäckbacken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567387</v>
+        <v>567433</v>
       </c>
       <c r="R2" t="n">
-        <v>6941075</v>
+        <v>6941222</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +775,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133807</t>
+          <t>https://artportalen.se/Sighting/137068024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81133809</v>
+        <v>81133807</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567368</v>
+        <v>567387</v>
       </c>
       <c r="R3" t="n">
-        <v>6940957</v>
+        <v>6941075</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,38 +888,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133809</t>
+          <t>https://artportalen.se/Sighting/81133807</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81133797</v>
+        <v>81133809</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567332</v>
+        <v>567368</v>
       </c>
       <c r="R4" t="n">
-        <v>6941150</v>
+        <v>6940957</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,54 +990,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133797</t>
+          <t>https://artportalen.se/Sighting/81133809</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81133798</v>
+        <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Marktjärn, Mpd</t>
+          <t>Matsäckbacken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567458</v>
+        <v>567350</v>
       </c>
       <c r="R5" t="n">
-        <v>6941245</v>
+        <v>6940948</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,24 +1091,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133798</t>
+          <t>https://artportalen.se/Sighting/137068021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81133802</v>
+        <v>81133797</v>
       </c>
       <c r="B6" t="n">
         <v>80432</v>
@@ -1123,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567395</v>
+        <v>567332</v>
       </c>
       <c r="R6" t="n">
-        <v>6941066</v>
+        <v>6941150</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,13 +1204,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133802</t>
+          <t>https://artportalen.se/Sighting/81133797</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81133805</v>
+        <v>81133798</v>
       </c>
       <c r="B7" t="n">
         <v>80432</v>
@@ -1225,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567399</v>
+        <v>567458</v>
       </c>
       <c r="R7" t="n">
-        <v>6941095</v>
+        <v>6941245</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,13 +1306,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133805</t>
+          <t>https://artportalen.se/Sighting/81133798</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81133806</v>
+        <v>81133802</v>
       </c>
       <c r="B8" t="n">
         <v>80432</v>
@@ -1327,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567379</v>
+        <v>567395</v>
       </c>
       <c r="R8" t="n">
-        <v>6941068</v>
+        <v>6941066</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,38 +1408,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133806</t>
+          <t>https://artportalen.se/Sighting/81133802</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81133796</v>
+        <v>81133805</v>
       </c>
       <c r="B9" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567333</v>
+        <v>567399</v>
       </c>
       <c r="R9" t="n">
-        <v>6941149</v>
+        <v>6941095</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1490,38 +1510,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133796</t>
+          <t>https://artportalen.se/Sighting/81133805</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81133799</v>
+        <v>81133806</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567454</v>
+        <v>567379</v>
       </c>
       <c r="R10" t="n">
-        <v>6941241</v>
+        <v>6941068</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1592,16 +1612,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133799</t>
+          <t>https://artportalen.se/Sighting/81133806</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>81133804</v>
+        <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>80467</v>
+        <v>79738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,34 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Marktjärn, Mpd</t>
+          <t>Matsäckbacken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567394</v>
+        <v>567368</v>
       </c>
       <c r="R11" t="n">
-        <v>6941097</v>
+        <v>6941061</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1683,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,27 +1713,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133804</t>
+          <t>https://artportalen.se/Sighting/137068022</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>81133808</v>
+        <v>81133796</v>
       </c>
       <c r="B12" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567394</v>
+        <v>567333</v>
       </c>
       <c r="R12" t="n">
-        <v>6941078</v>
+        <v>6941149</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1796,16 +1826,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133808</t>
+          <t>https://artportalen.se/Sighting/81133796</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>81133803</v>
+        <v>81133799</v>
       </c>
       <c r="B13" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567398</v>
+        <v>567454</v>
       </c>
       <c r="R13" t="n">
-        <v>6941081</v>
+        <v>6941241</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,16 +1928,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133803</t>
+          <t>https://artportalen.se/Sighting/81133799</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>81133800</v>
+        <v>81133804</v>
       </c>
       <c r="B14" t="n">
-        <v>57141</v>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,38 +1945,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Marktjärn, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567412</v>
+        <v>567394</v>
       </c>
       <c r="R14" t="n">
-        <v>6941204</v>
+        <v>6941097</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2004,16 +2030,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133800</t>
+          <t>https://artportalen.se/Sighting/81133804</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>81133794</v>
+        <v>81133808</v>
       </c>
       <c r="B15" t="n">
-        <v>99035</v>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567316</v>
+        <v>567394</v>
       </c>
       <c r="R15" t="n">
-        <v>6941074</v>
+        <v>6941078</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2106,16 +2132,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133794</t>
+          <t>https://artportalen.se/Sighting/81133808</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>81133810</v>
+        <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>99035</v>
+        <v>80608</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2123,34 +2149,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Marktjärn, Mpd</t>
+          <t>Matsäckbacken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567337</v>
+        <v>567367</v>
       </c>
       <c r="R16" t="n">
-        <v>6940943</v>
+        <v>6941061</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2177,12 +2203,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2197,27 +2233,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81133810</t>
+          <t>https://artportalen.se/Sighting/137068023</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81133801</v>
+        <v>81133803</v>
       </c>
       <c r="B17" t="n">
-        <v>97983</v>
+        <v>80468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567386</v>
+        <v>567398</v>
       </c>
       <c r="R17" t="n">
-        <v>6941060</v>
+        <v>6941081</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2309,6 +2345,418 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81133803</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>81133800</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567412</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6941204</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-08-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-10-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81133800</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>81133794</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567316</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6941074</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-08-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-10-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81133794</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>81133810</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567337</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6940943</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-08-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-10-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81133810</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>81133801</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567386</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6941060</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-08-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-10-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold, Anders Granér, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81133801</t>
         </is>
@@ -2332,6 +2780,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79777</v>
+        <v>79788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79788</v>
+        <v>79789</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57843-2024 artfynd.xlsx
+++ b/artfynd/A 57843-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068024</v>
       </c>
       <c r="B2" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137068021</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137068022</v>
       </c>
       <c r="B11" t="n">
-        <v>79791</v>
+        <v>79795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137068023</v>
       </c>
       <c r="B16" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
